--- a/Operations.xlsx
+++ b/Operations.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Micha\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/057e57f6e8780119/Desktop/Operations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7B77D9-9926-41D1-852F-FE198E571395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{1B7B77D9-9926-41D1-852F-FE198E571395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63F52C46-98DA-4C09-9937-B69FACBF0696}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Provoz" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Provoz!$A$1:$E$101</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -214,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -228,7 +231,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -448,7 +450,7 @@
     <col min="2" max="2" width="23" style="1" customWidth="1"/>
     <col min="3" max="3" width="17" style="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="1" customWidth="1"/>
-    <col min="5" max="5" width="70" style="5" customWidth="1"/>
+    <col min="5" max="5" width="70" customWidth="1"/>
     <col min="6" max="8" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -496,7 +498,7 @@
       <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -513,7 +515,7 @@
       <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -530,7 +532,7 @@
       <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -547,7 +549,7 @@
       <c r="D6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -564,7 +566,7 @@
       <c r="D7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -581,7 +583,7 @@
       <c r="D8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" t="s">
         <v>18</v>
       </c>
     </row>
@@ -598,7 +600,7 @@
       <c r="D9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" t="s">
         <v>19</v>
       </c>
     </row>
@@ -615,7 +617,7 @@
       <c r="D10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -632,7 +634,7 @@
       <c r="D11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" t="s">
         <v>20</v>
       </c>
     </row>
@@ -649,7 +651,7 @@
       <c r="D12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" t="s">
         <v>21</v>
       </c>
     </row>
@@ -666,7 +668,7 @@
       <c r="D13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" t="s">
         <v>22</v>
       </c>
     </row>
@@ -683,7 +685,7 @@
       <c r="D14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" t="s">
         <v>23</v>
       </c>
     </row>
@@ -700,7 +702,7 @@
       <c r="D15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" t="s">
         <v>24</v>
       </c>
     </row>
@@ -717,7 +719,7 @@
       <c r="D16" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" t="s">
         <v>25</v>
       </c>
     </row>
@@ -734,7 +736,7 @@
       <c r="D17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" t="s">
         <v>26</v>
       </c>
     </row>
@@ -751,7 +753,7 @@
       <c r="D18" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" t="s">
         <v>27</v>
       </c>
     </row>
@@ -768,7 +770,7 @@
       <c r="D19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" t="s">
         <v>18</v>
       </c>
     </row>
@@ -785,7 +787,7 @@
       <c r="D20" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" t="s">
         <v>28</v>
       </c>
     </row>
@@ -802,7 +804,7 @@
       <c r="D21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" t="s">
         <v>29</v>
       </c>
     </row>
@@ -819,7 +821,7 @@
       <c r="D22" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" t="s">
         <v>30</v>
       </c>
     </row>
@@ -836,7 +838,7 @@
       <c r="D23" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" t="s">
         <v>31</v>
       </c>
     </row>
@@ -853,7 +855,7 @@
       <c r="D24" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" t="s">
         <v>19</v>
       </c>
     </row>
@@ -870,7 +872,7 @@
       <c r="D25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" t="s">
         <v>13</v>
       </c>
     </row>
@@ -887,7 +889,7 @@
       <c r="D26" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" t="s">
         <v>22</v>
       </c>
     </row>
@@ -904,7 +906,7 @@
       <c r="D27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" t="s">
         <v>9</v>
       </c>
     </row>
@@ -921,7 +923,7 @@
       <c r="D28" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" t="s">
         <v>32</v>
       </c>
     </row>
@@ -938,7 +940,7 @@
       <c r="D29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" t="s">
         <v>21</v>
       </c>
     </row>
@@ -955,7 +957,7 @@
       <c r="D30" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" t="s">
         <v>33</v>
       </c>
     </row>
@@ -972,7 +974,7 @@
       <c r="D31" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -989,7 +991,7 @@
       <c r="D32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1006,7 +1008,7 @@
       <c r="D33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1023,7 +1025,7 @@
       <c r="D34" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1040,7 +1042,7 @@
       <c r="D35" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1057,7 +1059,7 @@
       <c r="D36" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1074,7 +1076,7 @@
       <c r="D37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1091,7 +1093,7 @@
       <c r="D38" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1108,7 +1110,7 @@
       <c r="D39" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1125,7 +1127,7 @@
       <c r="D40" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1142,7 +1144,7 @@
       <c r="D41" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E41" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1159,7 +1161,7 @@
       <c r="D42" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1176,7 +1178,7 @@
       <c r="D43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1193,7 +1195,7 @@
       <c r="D44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1210,7 +1212,7 @@
       <c r="D45" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1227,7 +1229,7 @@
       <c r="D46" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1244,7 +1246,7 @@
       <c r="D47" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="E47" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1261,7 +1263,7 @@
       <c r="D48" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="E48" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1278,7 +1280,7 @@
       <c r="D49" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="E49" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1295,7 +1297,7 @@
       <c r="D50" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="E50" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1312,7 +1314,7 @@
       <c r="D51" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="E51" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1329,7 +1331,7 @@
       <c r="D52" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="E52" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1346,7 +1348,7 @@
       <c r="D53" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="E53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1363,7 +1365,7 @@
       <c r="D54" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="E54" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1380,7 +1382,7 @@
       <c r="D55" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="E55" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1397,7 +1399,7 @@
       <c r="D56" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="E56" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1414,7 +1416,7 @@
       <c r="D57" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="E57" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1431,7 +1433,7 @@
       <c r="D58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="E58" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1448,7 +1450,7 @@
       <c r="D59" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="E59" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1465,7 +1467,7 @@
       <c r="D60" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="E60" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1482,7 +1484,7 @@
       <c r="D61" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="E61" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1499,7 +1501,7 @@
       <c r="D62" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="E62" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1516,7 +1518,7 @@
       <c r="D63" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E63" s="5" t="s">
+      <c r="E63" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1533,7 +1535,7 @@
       <c r="D64" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="E64" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1550,7 +1552,7 @@
       <c r="D65" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="E65" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1567,7 +1569,7 @@
       <c r="D66" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="E66" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1584,7 +1586,7 @@
       <c r="D67" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="E67" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1601,7 +1603,7 @@
       <c r="D68" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E68" s="5" t="s">
+      <c r="E68" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1618,7 +1620,7 @@
       <c r="D69" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="E69" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1635,7 +1637,7 @@
       <c r="D70" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E70" s="5" t="s">
+      <c r="E70" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1652,7 +1654,7 @@
       <c r="D71" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="E71" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1669,7 +1671,7 @@
       <c r="D72" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E72" s="5" t="s">
+      <c r="E72" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1686,7 +1688,7 @@
       <c r="D73" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E73" s="5" t="s">
+      <c r="E73" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1703,7 +1705,7 @@
       <c r="D74" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E74" s="5" t="s">
+      <c r="E74" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1720,7 +1722,7 @@
       <c r="D75" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E75" s="5" t="s">
+      <c r="E75" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1737,7 +1739,7 @@
       <c r="D76" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E76" s="5" t="s">
+      <c r="E76" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1754,7 +1756,7 @@
       <c r="D77" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E77" s="5" t="s">
+      <c r="E77" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1771,7 +1773,7 @@
       <c r="D78" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E78" s="5" t="s">
+      <c r="E78" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1788,7 +1790,7 @@
       <c r="D79" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E79" s="5" t="s">
+      <c r="E79" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1805,7 +1807,7 @@
       <c r="D80" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E80" s="5" t="s">
+      <c r="E80" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1822,7 +1824,7 @@
       <c r="D81" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E81" s="5" t="s">
+      <c r="E81" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1839,7 +1841,7 @@
       <c r="D82" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E82" s="5" t="s">
+      <c r="E82" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1856,7 +1858,7 @@
       <c r="D83" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E83" s="5" t="s">
+      <c r="E83" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1873,7 +1875,7 @@
       <c r="D84" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E84" s="5" t="s">
+      <c r="E84" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1890,7 +1892,7 @@
       <c r="D85" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E85" s="5" t="s">
+      <c r="E85" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1907,7 +1909,7 @@
       <c r="D86" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E86" s="5" t="s">
+      <c r="E86" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1924,7 +1926,7 @@
       <c r="D87" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E87" s="5" t="s">
+      <c r="E87" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1941,7 +1943,7 @@
       <c r="D88" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E88" s="5" t="s">
+      <c r="E88" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1958,7 +1960,7 @@
       <c r="D89" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E89" s="5" t="s">
+      <c r="E89" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1975,7 +1977,7 @@
       <c r="D90" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E90" s="5" t="s">
+      <c r="E90" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1992,7 +1994,7 @@
       <c r="D91" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E91" s="5" t="s">
+      <c r="E91" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2009,7 +2011,7 @@
       <c r="D92" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E92" s="5" t="s">
+      <c r="E92" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2026,7 +2028,7 @@
       <c r="D93" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E93" s="5" t="s">
+      <c r="E93" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2043,7 +2045,7 @@
       <c r="D94" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E94" s="5" t="s">
+      <c r="E94" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2060,7 +2062,7 @@
       <c r="D95" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E95" s="5" t="s">
+      <c r="E95" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2077,7 +2079,7 @@
       <c r="D96" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E96" s="5" t="s">
+      <c r="E96" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2094,7 +2096,7 @@
       <c r="D97" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E97" s="5" t="s">
+      <c r="E97" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2111,7 +2113,7 @@
       <c r="D98" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E98" s="5" t="s">
+      <c r="E98" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2128,7 +2130,7 @@
       <c r="D99" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E99" s="5" t="s">
+      <c r="E99" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2145,7 +2147,7 @@
       <c r="D100" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E100" s="5" t="s">
+      <c r="E100" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2162,11 +2164,12 @@
       <c r="D101" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E101" s="5" t="s">
+      <c r="E101" t="s">
         <v>32</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E101" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <dataValidations count="1">
     <dataValidation type="list" sqref="D2:D101" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Provoz,Údržba,Porucha"</formula1>
